--- a/data/sentiment/CNN Fear and Greed Index.xlsx
+++ b/data/sentiment/CNN Fear and Greed Index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/sentiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C30EB64-A162-314F-A052-E08C54D74E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F47D4A2-6601-354D-BA18-FF8B82F6F5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4540" yWindow="2700" windowWidth="27640" windowHeight="16680" xr2:uid="{4DB5C0D8-73A9-F241-BE73-FF8556E11991}"/>
   </bookViews>
@@ -618,7 +618,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -662,6 +662,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -680,11 +688,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -699,9 +708,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1034,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF0C9EB-215E-3E47-AC49-550A89FC547A}">
-  <dimension ref="A1:B3835"/>
+  <dimension ref="A1:B3838"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
@@ -31719,6 +31730,30 @@
       </c>
       <c r="B3835" s="5">
         <v>45.49</v>
+      </c>
+    </row>
+    <row r="3836" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3836" s="2">
+        <v>46013</v>
+      </c>
+      <c r="B3836" s="5">
+        <v>57.29</v>
+      </c>
+    </row>
+    <row r="3837" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3837" s="2">
+        <v>46014</v>
+      </c>
+      <c r="B3837" s="5">
+        <v>57.71</v>
+      </c>
+    </row>
+    <row r="3838" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3838" s="2">
+        <v>46015</v>
+      </c>
+      <c r="B3838" s="5">
+        <v>58.23</v>
       </c>
     </row>
   </sheetData>
@@ -31735,11 +31770,14 @@
       <c r="B2" t="s">
         <v>188</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>189</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{91C9E8C5-DFBB-8342-A3CF-62E1CFDD7651}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/sentiment/CNN Fear and Greed Index.xlsx
+++ b/data/sentiment/CNN Fear and Greed Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/sentiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F47D4A2-6601-354D-BA18-FF8B82F6F5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A07AB7-97B2-FC45-BA27-F0C8CCB7F024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4540" yWindow="2700" windowWidth="27640" windowHeight="16680" xr2:uid="{4DB5C0D8-73A9-F241-BE73-FF8556E11991}"/>
   </bookViews>
@@ -1045,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF0C9EB-215E-3E47-AC49-550A89FC547A}">
-  <dimension ref="A1:B3838"/>
+  <dimension ref="A1:B3839"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
@@ -31754,6 +31754,14 @@
       </c>
       <c r="B3838" s="5">
         <v>58.23</v>
+      </c>
+    </row>
+    <row r="3839" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3839" s="2">
+        <v>46017</v>
+      </c>
+      <c r="B3839" s="5">
+        <v>55.51</v>
       </c>
     </row>
   </sheetData>

--- a/data/sentiment/CNN Fear and Greed Index.xlsx
+++ b/data/sentiment/CNN Fear and Greed Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/sentiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DABA24D-A694-D14D-B4C9-4632C1536657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCA0BAB-6023-7C4F-BCFD-D83D68A39642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16940" yWindow="780" windowWidth="19080" windowHeight="20700" xr2:uid="{4DB5C0D8-73A9-F241-BE73-FF8556E11991}"/>
+    <workbookView xWindow="16920" yWindow="780" windowWidth="19080" windowHeight="20700" xr2:uid="{4DB5C0D8-73A9-F241-BE73-FF8556E11991}"/>
   </bookViews>
   <sheets>
     <sheet name="CNNFNGI" sheetId="1" r:id="rId1"/>
@@ -1053,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF0C9EB-215E-3E47-AC49-550A89FC547A}">
-  <dimension ref="A1:C3841"/>
+  <dimension ref="A1:C3844"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
@@ -43310,6 +43310,39 @@
       </c>
       <c r="C3841" s="5">
         <v>48.91</v>
+      </c>
+    </row>
+    <row r="3842" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3842" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B3842" s="2">
+        <v>46022</v>
+      </c>
+      <c r="C3842" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3843" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3843" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B3843" s="2">
+        <v>46023</v>
+      </c>
+      <c r="C3843" s="5">
+        <v>44.83</v>
+      </c>
+    </row>
+    <row r="3844" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3844" s="2">
+        <v>46024</v>
+      </c>
+      <c r="B3844" s="2">
+        <v>46024</v>
+      </c>
+      <c r="C3844" s="5">
+        <v>44.63</v>
       </c>
     </row>
   </sheetData>

--- a/data/sentiment/CNN Fear and Greed Index.xlsx
+++ b/data/sentiment/CNN Fear and Greed Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB03E77-2BA1-4765-AABB-383FBC4731D0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35860E32-23FA-4372-A3FF-041246C5031A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16920" yWindow="780" windowWidth="19080" windowHeight="20700" xr2:uid="{4DB5C0D8-73A9-F241-BE73-FF8556E11991}"/>
   </bookViews>
@@ -653,18 +653,24 @@
     <font>
       <sz val="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1054,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF0C9EB-215E-3E47-AC49-550A89FC547A}">
-  <dimension ref="A1:E3846"/>
+  <dimension ref="A1:E3848"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="4" bestFit="1" customWidth="1"/>
@@ -71221,6 +71227,57 @@
         <v>52</v>
       </c>
     </row>
+    <row r="3847" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3847" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B3847" s="4">
+        <v>46029</v>
+      </c>
+      <c r="C3847" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D3847" s="4" t="str">
+        <f t="shared" ref="D3847:D3848" si="61">IF(
+ AND(
+  B3847 &gt;= IF(
+         YEAR(B3847)&gt;=2007,
+         DATE(YEAR(B3847),3,14)-WEEKDAY(DATE(YEAR(B3847),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B3847),4,7)-WEEKDAY(DATE(YEAR(B3847),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B3847 &lt;  IF(
+         YEAR(B3847)&gt;=2007,
+         DATE(YEAR(B3847),11,7)-WEEKDAY(DATE(YEAR(B3847),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B3847),10,31)-WEEKDAY(DATE(YEAR(B3847),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-5</v>
+      </c>
+      <c r="E3847" s="5">
+        <v>43.69</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3848" s="4">
+        <v>46030</v>
+      </c>
+      <c r="B3848" s="4">
+        <v>46030</v>
+      </c>
+      <c r="C3848" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D3848" s="4" t="str">
+        <f t="shared" si="61"/>
+        <v>UTC-5</v>
+      </c>
+      <c r="E3848" s="5">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
